--- a/docs/import-samples/05_CAPACITY_EXCEEDED_no_room_large_enough_auto.xlsx
+++ b/docs/import-samples/05_CAPACITY_EXCEEDED_no_room_large_enough_auto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\PTIT DOC\IST\UCAS\docs\import-samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE4071B-EDD0-4BA5-BD71-65842670213D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D831117F-F63E-4D13-B447-6C324EF84C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23385" yWindow="5370" windowWidth="17280" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timetable_import" sheetId="1" r:id="rId1"/>
